--- a/data_lake/industry/CFM/UFS.xlsx
+++ b/data_lake/industry/CFM/UFS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9636E27B-95F7-405E-9CAF-30DAD6848C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB100BA-A3E4-42A2-8ADB-1B5B72FB46C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,31 +70,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -103,9 +103,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,45 +132,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -448,19 +453,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -506,7 +511,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -529,7 +534,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -552,7 +557,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -575,7 +580,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -598,7 +603,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -621,7 +626,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -644,7 +649,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -667,7 +672,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -690,7 +695,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -713,7 +718,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -736,7 +741,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -759,7 +764,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -782,7 +787,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -805,7 +810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -828,7 +833,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -851,7 +856,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -874,7 +879,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -897,7 +902,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -920,7 +925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -943,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -966,7 +971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -989,7 +994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1012,7 +1017,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1035,7 +1040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1058,7 +1063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1081,7 +1086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1104,7 +1109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1127,7 +1132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1150,7 +1155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1173,7 +1178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1196,7 +1201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1219,7 +1224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1242,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1265,7 +1270,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1288,7 +1293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1311,7 +1316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1334,7 +1339,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1357,7 +1362,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1380,7 +1385,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1403,7 +1408,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1426,7 +1431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1449,7 +1454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1472,7 +1477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1495,7 +1500,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1518,7 +1523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1541,7 +1546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1561,6 +1566,121 @@
         <v>28</v>
       </c>
       <c r="G48" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F49" s="9">
+        <v>28</v>
+      </c>
+      <c r="G49" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F50" s="9">
+        <v>28</v>
+      </c>
+      <c r="G50" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F51" s="9">
+        <v>28</v>
+      </c>
+      <c r="G51" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F52" s="9">
+        <v>28</v>
+      </c>
+      <c r="G52" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F53" s="9">
+        <v>28</v>
+      </c>
+      <c r="G53" s="9">
         <v>27</v>
       </c>
     </row>
@@ -1572,19 +1692,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9244C5-F48F-43B7-9154-783F9DA9F8C6}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1630,7 +1750,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1653,7 +1773,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1676,7 +1796,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1699,7 +1819,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1722,7 +1842,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1745,7 +1865,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1768,7 +1888,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1791,7 +1911,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1814,7 +1934,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1837,7 +1957,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1860,7 +1980,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1883,7 +2003,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1906,7 +2026,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1929,7 +2049,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1952,7 +2072,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1975,7 +2095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1998,7 +2118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2021,7 +2141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2044,7 +2164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2067,7 +2187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2090,7 +2210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2113,7 +2233,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2136,7 +2256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2159,7 +2279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2182,7 +2302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2205,7 +2325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2228,7 +2348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2251,7 +2371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2274,7 +2394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2297,7 +2417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2320,7 +2440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2343,7 +2463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2366,7 +2486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2389,7 +2509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2412,7 +2532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2435,7 +2555,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2458,7 +2578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2481,7 +2601,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2504,7 +2624,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2527,7 +2647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2550,7 +2670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2573,7 +2693,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2596,7 +2716,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2619,7 +2739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2642,7 +2762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2665,7 +2785,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2685,6 +2805,121 @@
         <v>35.5</v>
       </c>
       <c r="G48" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F49" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G49" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F50" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G50" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F51" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G51" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F52" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G52" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F53" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G53" s="12">
         <v>33</v>
       </c>
     </row>
@@ -2696,19 +2931,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6478684B-CAE8-48EE-80F6-6A07A9D856F1}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2731,7 +2966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2754,7 +2989,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2777,7 +3012,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2800,7 +3035,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2823,7 +3058,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2846,7 +3081,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2869,7 +3104,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2892,7 +3127,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2915,7 +3150,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2938,7 +3173,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2961,7 +3196,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2984,7 +3219,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3007,7 +3242,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3030,7 +3265,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3053,7 +3288,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3076,7 +3311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3099,7 +3334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3122,7 +3357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3145,7 +3380,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3168,7 +3403,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3191,7 +3426,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3214,7 +3449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3237,7 +3472,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3260,7 +3495,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3283,7 +3518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3306,7 +3541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3329,7 +3564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3352,7 +3587,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3375,7 +3610,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3398,7 +3633,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3421,7 +3656,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3444,7 +3679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3467,7 +3702,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3490,7 +3725,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3513,7 +3748,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3536,7 +3771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3559,7 +3794,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3582,7 +3817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3605,7 +3840,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3628,7 +3863,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3651,7 +3886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3674,7 +3909,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3697,7 +3932,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3720,7 +3955,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3743,7 +3978,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3766,7 +4001,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3789,7 +4024,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3809,6 +4044,121 @@
         <v>63</v>
       </c>
       <c r="G48" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F49" s="9">
+        <v>63</v>
+      </c>
+      <c r="G49" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F50" s="9">
+        <v>63</v>
+      </c>
+      <c r="G50" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F51" s="9">
+        <v>63</v>
+      </c>
+      <c r="G51" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F52" s="9">
+        <v>63</v>
+      </c>
+      <c r="G52" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F53" s="9">
+        <v>63</v>
+      </c>
+      <c r="G53" s="9">
         <v>60</v>
       </c>
     </row>
@@ -3820,19 +4170,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9291558D-A342-4E30-81D9-3EB746F72AE7}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3855,7 +4205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3878,7 +4228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3901,7 +4251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3924,7 +4274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3947,7 +4297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3970,7 +4320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3993,7 +4343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4016,7 +4366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4039,7 +4389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4062,7 +4412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4085,7 +4435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4108,7 +4458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4131,7 +4481,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4154,7 +4504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4177,7 +4527,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4200,7 +4550,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4223,7 +4573,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4246,7 +4596,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4269,7 +4619,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4292,7 +4642,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4315,7 +4665,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4338,7 +4688,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4361,7 +4711,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4384,7 +4734,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4407,7 +4757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4430,7 +4780,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4453,7 +4803,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4476,7 +4826,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4499,7 +4849,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4522,7 +4872,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4545,7 +4895,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4568,7 +4918,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4591,7 +4941,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4614,7 +4964,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4637,7 +4987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4660,7 +5010,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4683,7 +5033,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4706,7 +5056,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4729,7 +5079,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -4752,7 +5102,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -4775,7 +5125,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -4798,7 +5148,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -4821,7 +5171,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -4844,7 +5194,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -4867,7 +5217,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4890,7 +5240,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4913,7 +5263,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4933,6 +5283,121 @@
         <v>93</v>
       </c>
       <c r="G48" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>93</v>
+      </c>
+      <c r="G49" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>93</v>
+      </c>
+      <c r="G50" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>93</v>
+      </c>
+      <c r="G51" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>93</v>
+      </c>
+      <c r="G52" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>93</v>
+      </c>
+      <c r="G53" s="9">
         <v>90</v>
       </c>
     </row>
